--- a/public/Bulk_Device_Template.xlsx
+++ b/public/Bulk_Device_Template.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="arsalan"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10913"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macworld/Desktop/dms-app/public/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB80CFEB-D6C3-E340-9270-D1FFAD5AB731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="0" windowHeight="0" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16080" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:revision xmlns:pm="smNativeData" day="1724167691" val="1216" rev="124" revOS="4" revMin="124" revMax="0"/>
@@ -40,32 +45,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;£&quot;;\-#,##0\ &quot;£&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;£&quot;;[Red]\-#,##0\ &quot;£&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;£&quot;;\-#,##0.00\ &quot;£&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;£&quot;;[Red]\-#,##0.00\ &quot;£&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;£&quot;_-;\-* #,##0\ &quot;£&quot;_-;_-* &quot;-&quot;\ &quot;£&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _£_-;\-* #,##0\ _£_-;_-* &quot;-&quot;\ _£_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;£&quot;_-;\-* #,##0.00\ &quot;£&quot;_-;_-* &quot;-&quot;??\ &quot;£&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _£_-;\-* #,##0.00\ _£_-;_-* &quot;-&quot;??\ _£_-;_-@_-"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1724167691" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
   </fonts>
   <fills count="2">
@@ -78,36 +64,32 @@
   </fills>
   <borders count="1">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1724167691"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
       <pm:charStyles xmlns:pm="smNativeData" id="1724167691" count="1">
         <pm:charStyle name="Normal" fontId="0"/>
@@ -372,14 +354,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="9" defaultColWidth="10.000000" defaultRowHeight="13.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="11.108108" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" customWidth="1"/>
+    <col min="4" max="4" width="10" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -389,30 +372,13 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1724167691" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.787500" right="0.787500" top="0.787500" bottom="0.787500" header="0.393750" footer="0.393750"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1" pageOrder="overThenDown"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1724167691" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1724167691" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1724167691" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1724167691" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="0.78749999999999998" bottom="0.78749999999999998" header="0.39374999999999999" footer="0.39374999999999999"/>
+  <pageSetup paperSize="9" fitToWidth="0" pageOrder="overThenDown" orientation="portrait"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1724167691" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
